--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -37,35 +37,45 @@
     <t>I am a peanut grower in Peanut Basin, Senegal. For this season, how much yield can I expect?</t>
   </si>
   <si>
-    <t>You’re now in the early‑flowering phase of your sunflower crop – the stage when a side‑dress of nitrogen gives the biggest boost to seed set and oil quality. Because the soil is a slightly acidic clay‑loam with modest organic matter and total nitrogen around 0.15 %, a second nitrogen application is needed, but it should be moderate to avoid excess vegetative growth that can lower oil quality.
-For a 3‑ha field, aim for about 30 kg of nitrogen per hectare at this stage, which works out to roughly 90 kg of nitrogen total. Using common urea (46 % N), that means applying about 195 kg of urea (≈ 65 kg per hectare). Spread the granules evenly and incorporate them into the top 5–7 cm, or place them in shallow furrows, to reduce the risk of runoff now that a rainy spell (about 70 mm over the next nine days, with a peak on 29 May) is on the way. If you can apply today or within the next couple of days, the soil will still be able to absorb the nutrient before the heaviest rains arrive.
-Keep an eye on the field for any signs of lodging as the soil stays moist, and if you notice excessive weed growth, a light post‑emergence herbicide can be used safely after the nitrogen has been incorporated. This split‑application strategy should help you reach higher yields while maintaining the quality needed for premium sunflower oil.</t>
-  </si>
-  <si>
-    <t>In the Aurangabad region, sunflower plants that are already in the first week of August are typically at the early‑bud to early‑flower stage. At this point the crop can still benefit from a top‑dressing of nitrogen, which is the most important nutrient for boosting seed size and overall yield, while also helping to maintain a good oil‑to‑protein ratio.
-For a high‑quality oil crop, aim for a total nitrogen application of **60 – 90 kg N ha⁻¹**. Because the basal dose was already applied at sowing, the remaining nitrogen should be supplied now as a split top‑dress. Use about **30 – 45 kg N ha⁻¹** (≈ 65–75 % of the total recommended rate) in the form of urea (46 % N) or calcium nitrate, applied uniformly over the field and incorporated lightly with a shallow harrow or by irrigation. This timing coincides with rapid seed‑filling and will encourage larger kernels without diluting oil content.
-Do not exceed 120 kg N ha⁻¹, as excessive nitrogen can increase protein at the expense of oil quality and may promote lodging in the later stages. After application, watch the foliage: a healthy deep‑green color indicates adequate N, while yellowing suggests a shortfall. If possible, a quick leaf‑N test or chlorophyll meter reading can fine‑tune the rate, but the 60‑90 kg N ha⁻¹ range is a reliable guideline for most fields in Chhatrapati Sambhajinagar.</t>
-  </si>
-  <si>
-    <t>The amount of peanuts you can harvest this season depends on many factors that are not captured in the brief information you provided. In the Kaolack (Peanut Basin) region, typical yields for well‑managed farms range from about 1.5 t ha⁻¹ to 2.5 t ha⁻¹, but actual results can be higher or lower depending on the variety you planted, the quality of the seed, planting density, fertilizer use, pest and disease pressure, and the rainfall pattern you have experienced so far.
-Because I do not have details on the specific cultivar, the inputs you are applying, the condition of your fields, or the weather trends for the current growing season, I cannot give you a precise figure for your farm. If you can share information such as the seed variety, planting date, fertilizer program, and any observations of pests or water stress, I can narrow the estimate and suggest management adjustments to help you reach the upper end of the typical yield range. 
-In the meantime, monitoring soil moisture, scouting for early signs of leaf spot or nematodes, and ensuring timely fertilizer applications are the most reliable ways to maximize your peanut harvest in Kaolack. Feel free to provide more details, and I’ll be glad to refine the yield projection for you.</t>
-  </si>
-  <si>
-    <t>You’re most likely still in the early vegetative stage – seedlings are just getting established and the crop will need a good boost of nutrients and moisture to reach its potential. In the Peanut Basin, a well‑managed peanut field on fertile, well‑watered soils can give 1.5 – 2.5 t ha⁻¹, but the conditions you’ve described pull the expectation down. Your soil is very low in organic matter and nitrogen, and the seasonal forecast is below normal with no rain in the coming days, so water stress will be a limiting factor unless you can capture any early showers or apply supplemental irrigation.
-If you follow the recommended nitrogen program (about 50–75 kg N ha⁻¹ at planting and a top‑dress of 100–150 kg N ha⁻¹ around V4‑V6) and add 5–10 t ha⁻¹ of compost or manure to raise organic matter, you can expect roughly 1.0 – 1.3 t ha⁻¹ of marketable peanuts. On your 3 ha farm that translates to about 3 – 4 t of grain at harvest. If fertilizer and organic amendments are limited, yields could fall to 0.6 – 0.8 t ha⁻¹, so the most important actions now are to secure the nitrogen applications and, if possible, retain any crop residues as mulch to conserve soil moisture. Keeping the field weed‑free and monitoring for early pest pressure will also help protect the modest yield you can achieve under the drier season.</t>
-  </si>
-  <si>
-    <t>Your maize is now at the knee‑high to early tasseling stage, the point when Fall Armyworm (FAW) can quickly damage the growing point if not checked. Because you have a rainy spell this week (about nine wet days ahead) you’ll need to act while the foliage can dry for a short window after spraying.
-First, walk the field and count larvae in the whorl and on the lower leaves. If you see more than one active larva per plant, treatment is warranted. For a small‑scale (3 ha) farm the safest first line is a biopesticide: a neem‑seed‑oil spray (2 % v/v) or a Bacillus thuringiensis (Bt) formulation at the label rate. Both work well on early instars, are cheap, break down quickly in the moist soil you have, and pose little risk to you or the environment. Apply in the early morning or late afternoon when the leaves are dry, and try to keep rain off the spray for at least 24 hours.
-If the infestation is heavy (several larvae per plant) and the biopesticide won’t keep up, a short‑acting synthetic such as lambda‑cyhalothrin (or chlorpyrifos where allowed) can be used. Follow the label strictly, wear gloves and a mask, and respect the pre‑harvest interval. Because your soil is slightly acidic (pH 5.8) and holds water well, avoid over‑fertilising with nitrogen – the moderate N recommendation you already have is enough and will not encourage more pests.
-Finally, destroy any heavily infested plants, keep the field clean of crop residues, and consider planting a FAW‑resistant hybrid next season. This integrated approach should keep the pest under control while fitting the rainy conditions and your farm’s resources.</t>
-  </si>
-  <si>
-    <t>In Kitale’s mid‑June climate the Fall Armyworm (Spodoptera frugiperda) is at its peak, so rapid action is essential to protect your maize. Begin by scouting the whole field each morning; any plant showing ragged leaf edges, “window‑pane” damage or a single dead leaf should be inspected for larvae. When you locate larvae, pick them off by hand in the early morning when they are less active, crush them and destroy them in a fire‑proof container. This cultural step can reduce the population by 30‑40 % before chemicals are needed.
-For a biological push, apply a Bacillus thuringiensis (Bt) formulation that is registered for maize in Kenya. Spray the product at the recommended rate when larvae are still small (first‑instar to third‑instar) and repeat after 7‑10 days if you still see active feeding. Neem‑seed oil can be mixed with water and sprayed as a secondary bio‑insecticide; it works best on early instars and also deters adult moths from laying eggs.
-If the infestation exceeds the economic threshold (≈1 larva per 10 m²) or the crop is already showing extensive damage, use a registered chemical such as spinosad, emamectin benzoate, or chlorantraniliprole. Apply the insecticide in the cooler part of the day, follow the label dose, and observe the pre‑harvest interval to avoid residue problems. Rotate between products with different modes of action to delay resistance.
-After treatment, continue weekly scouting for at least three weeks. Combine these steps—hand‑picking, Bt or neem, and, when necessary, a judicious chemical spray—with good field hygiene (removing crop residues and weeds) to keep Fall Armyworm under control and safeguard your maize yield.</t>
+    <t>Given the time of year here, your maize is likely in mid‑vegetative stage (knee‑ to waist‑high). Fall armyworm can still be stopped now if you act quickly and target the larvae in the whorl.
+First, scout before you spray. Walk the field and check 5 spots, 10 plants per spot. If about 2 or more in every 10 have fresh “windowing” and frass with live caterpillars, treat the whole field. If damage is only in patches, focus treatments there.
+Use products that work inside the whorl and on younger larvae. Good options are:
+- Bacillus thuringiensis (Bt kurstaki): 20–30 g per 20 L water, directed into the whorl.
+- Emamectin benzoate 5% SG: 6 g per 20 L.
+- Chlorantraniliprole 200 g/L: 4–5 ml per 20 L.
+- Spinetoram 120 g/L: 6 ml per 20 L.
+Choose one and follow the label. Avoid relying on pyrethroids alone; resistance is common. Rotate to a different mode of action if a second spray is needed.
+Spray early morning or late afternoon, on a calm, dry period. Use enough water to reach deep into the funnel (about 200–300 L per hectare; roughly 10–15 knapsacks of 20 L per hectare). A small amount of liquid soap in the tank helps wetting. For small hotspots, you can also crush larvae or drop a pinch of dry sand/ash into the whorl to injure them.
+Check again after 3–4 days. If fresh damage with live larvae continues, repeat with a different product in 7–10 days. Wear gloves and a mask, keep spray off flowers, and don’t spray when bees are active.</t>
+  </si>
+  <si>
+    <t>Fall armyworm spreads fast in June here, so act immediately. Scout twice weekly early morning or evening across the field (at least 5 spots, 10 plants each). Look for fresh “sawdust” frass in the whorl and live larvae. Focus control on small larvae; older plants and large larvae are harder to kill.
+If infestation is light and larvae are small, do quick, low-cost measures. Crush egg masses and larger caterpillars by hand. Put a small pinch (about a teaspoon) of dry fine sand or wood ash directly into the whorl of infested plants; it abrades and dries larvae. Repeat after rain. Avoid piling on leaves; target the funnel.
+Biological options work best on young larvae. Spray Bacillus thuringiensis (Bt) or spinosad/spinetoram products directed into the whorl in the late afternoon or evening when larvae are active. Ensure good coverage into the funnel and reapply after 5–7 days if fresh damage continues.
+If many plants are freshly damaged with live larvae, use a registered insecticide and rotate modes of action to slow resistance. Effective actives include emamectin benzoate, chlorantraniliprole, or indoxacarb; avoid relying only on pyrethroids. Apply with a knapsack using a narrow jet straight into the whorl; add a wetting/sticking agent as per label. Spray in calm, cool hours, follow label rates, wear PPE, and avoid drift.
+Going forward, plant early, keep fields weed-free and well-nourished, conserve beneficial insects by avoiding unnecessary broad-spectrum sprays, and consider push–pull (desmodium with Napier/Brachiaria) to reduce future FAW pressure. Continue monitoring even after treatment.</t>
+  </si>
+  <si>
+    <t>For high yield with good oil quality in sunflower, keep nitrogen moderate and split. In Ballari conditions, apply 45–60 kg N/ha under rainfed crop and 60–80 kg N/ha under irrigated crop. Do not exceed about 80–90 kg N/ha, as excess nitrogen reduces oil percentage and can delay maturity. As a guide, 60 kg N/ha equals about 130 kg urea/ha (≈53 kg urea/acre); 80 kg N/ha equals about 174 kg urea/ha (≈70 kg urea/acre).
+Apply nitrogen in two splits: half as basal at sowing and the remaining half at 25–30 days after sowing, before button/budding. If your crop is around 3–4 weeks old now, complete the second split immediately and irrigate lightly (or apply before a rain). If the crop has already reached button stage or flowering, avoid further nitrogen topdressing to protect oil content.
+Place fertilizer in bands 5–7 cm away from the row and 3–5 cm deep; avoid contact with stems/leaves to prevent scorch. Maintain good weed control so applied nitrogen benefits the crop, not weeds.
+For oil quality, the key is balanced, timely nutrition. Keep nitrogen within the ranges above and, if possible, ensure adequate sulfur (about 15–20 kg S/ha from gypsum or other sources) to enhance oil content and seed filling.</t>
+  </si>
+  <si>
+    <t>Given it’s early August, your kharif sunflower is likely in early to mid-vegetative stage moving toward bud initiation. For good yield without sacrificing oil percentage, keep nitrogen moderate rather than heavy.
+Aim for a total of about 60 kg N per hectare if you’re rainfed. If you have dependable irrigation and the crop is growing strongly, you can go up to 80 kg N/ha, but avoid pushing beyond 90 kg N/ha as that tends to dilute oil content. Split the nitrogen: half as a basal dose at sowing and the other half at 25–30 days after sowing, around the 6–8 leaf stage. If you missed the basal, side-dress 30 kg N/ha now and the remaining 30 kg N/ha before visible bud formation. Stop nitrogen once buds are visible to protect oil quality.
+Place the top-dress in a band 8–10 cm away from the row and 5–7 cm deep, into moist soil, and keep it off the stem. If using urea, 60 kg N/ha equals about 130 kg urea/ha; split roughly 65 kg/ha per application. For an 80 kg N/ha program, that’s about 174 kg urea/ha, split around 87 kg/ha each time. Incorporate lightly or apply just before irrigation, and avoid applying onto very dry soil or where runoff is likely. If the crop is already dark green and very lush, hold the top-dress to avoid lodging and lower oil; if it’s pale and thin, give the full planned split.</t>
+  </si>
+  <si>
+    <t>With only location, crop and date, I can’t give a reliable peanut yield estimate for this season in Kaolack. Yields vary widely and depend on several factors: variety, sowing date and plant population, rainfall timing and distribution, soil fertility and inoculation, weed/pest/disease pressure, and harvest timing/curing. Without those details, any number would be a guess.
+If you share the variety, sowing date, row spacing and within-row spacing (or plants per square meter), fertilizer/manure and rhizobium inoculant use, current weed/pest/disease status, and your field’s recent yields, I can provide a realistic range and highlight key risks and opportunities for this season.
+Meanwhile, you can build an on-field estimate as the crop develops. At early pod fill and again 2–3 weeks before harvest, select three representative spots. In each, measure a known row length (for example, 10 meters), count the plants, then harvest all marketable pods from 10 average plants, remove excess soil, and weigh the pods. Calculate average pod weight per plant, multiply by plants per hectare (derived from your spacing and stand), and adjust for expected harvest losses and drying to final market moisture. Averaging across spots will give a practical yield expectation tailored to your field.
+Send the details above, and I’ll help translate them into an expected yield range for your farm.</t>
+  </si>
+  <si>
+    <t>At this point in the season you’re likely at planting or early establishment. With that in mind, a realistic yield range in the Peanut Basin this year is about 0.8–1.2 t/ha. With strong management you can push toward 1.5–2.0 t/ha; in a tough season it could slip to 0.5–0.8 t/ha. On your 3 hectares, that’s roughly 2.4–3.6 tons typical, up to about 4.5–6.0 tons with good practices.
+To stay on the higher end, focus on a full, even stand and early weed control. Close gaps promptly and weed twice early to protect moisture and reduce competition. Feed the crop mainly with phosphorus and calcium rather than heavy nitrogen. At planting, band 100–150 kg/ha of single superphosphate (or an equivalent P source) a few centimeters to the side of the seed. If you used a compound fertilizer, keep nitrogen modest; excess N reduces nodulation and yield. If seed was not inoculated, apply a groundnut-specific inoculant as soon as possible on any replanting. At early flowering/pegging, broadcast 200–300 kg/ha of gypsum to supply calcium for pod fill. Keep crop residues or light mulch on the soil surface to conserve moisture and moderate soil temperature.
+Watch for early leaf spots and aphids; if disease pressure builds, start a protective spray program promptly. Harvest on time once the majority of pods are mature to avoid losses. If you hit these points, you’ll give yourself the best chance of landing in the upper part of the range.</t>
   </si>
 </sst>
 </file>
@@ -431,15 +441,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="339.6" customHeight="1">
+    <row r="2" spans="1:3" ht="373.8" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="271.8" customHeight="1">
@@ -447,10 +457,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="281.39999999999998" customHeight="1">
@@ -458,10 +468,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
